--- a/IPC_Regiones_Divisiones.xlsx
+++ b/IPC_Regiones_Divisiones.xlsx
@@ -458,7 +458,7 @@
         <v>115.6843833269237</v>
       </c>
       <c r="E2" s="2">
-        <v>0.1435582</v>
+        <v>0.1435581999999999</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -472,7 +472,7 @@
         <v>0.1411751168406556</v>
       </c>
       <c r="D3" s="2">
-        <v>114.4526276680617</v>
+        <v>114.4526276680616</v>
       </c>
       <c r="E3" s="2">
         <v>0.1411751168406556</v>
@@ -492,7 +492,7 @@
         <v>115.1895201239744</v>
       </c>
       <c r="E4" s="2">
-        <v>0.02116955241080869</v>
+        <v>0.02116955241080868</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -509,7 +509,7 @@
         <v>115.79119381048</v>
       </c>
       <c r="E5" s="2">
-        <v>0.03105379528768681</v>
+        <v>0.03105379528768679</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -520,13 +520,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2">
-        <v>0.03717274249100482</v>
+        <v>0.03717274249100481</v>
       </c>
       <c r="D6" s="2">
-        <v>116.892578624805</v>
+        <v>116.8925786248049</v>
       </c>
       <c r="E6" s="2">
-        <v>0.03717274249100483</v>
+        <v>0.0371727424910048</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -540,10 +540,10 @@
         <v>0.0316799930531572</v>
       </c>
       <c r="D7" s="2">
-        <v>115.7385888621268</v>
+        <v>115.7385888621269</v>
       </c>
       <c r="E7" s="2">
-        <v>0.03167999305315721</v>
+        <v>0.03167999305315718</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -554,13 +554,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2">
+        <v>0.01407284297814614</v>
+      </c>
+      <c r="D8" s="2">
+        <v>116.0741668374778</v>
+      </c>
+      <c r="E8" s="2">
         <v>0.01407284297814613</v>
-      </c>
-      <c r="D8" s="2">
-        <v>116.0741668374777</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.01407284297814614</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -574,10 +574,10 @@
         <v>0.01760686795995203</v>
       </c>
       <c r="D9" s="2">
-        <v>115.0264386249908</v>
+        <v>115.0264386249907</v>
       </c>
       <c r="E9" s="2">
-        <v>0.01760686795995204</v>
+        <v>0.01760686795995203</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -588,13 +588,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="2">
-        <v>0.05497800000000001</v>
+        <v>0.05497800000000002</v>
       </c>
       <c r="D10" s="2">
         <v>105.619782443459</v>
       </c>
       <c r="E10" s="2">
-        <v>0.05497800000000002</v>
+        <v>0.05497799999999999</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -611,7 +611,7 @@
         <v>109.9649037341776</v>
       </c>
       <c r="E11" s="2">
-        <v>0.05839271367525364</v>
+        <v>0.0583927136752536</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -625,10 +625,10 @@
         <v>0.01138460064468043</v>
       </c>
       <c r="D12" s="2">
-        <v>109.37265258337</v>
+        <v>109.3726525833701</v>
       </c>
       <c r="E12" s="2">
-        <v>0.01138460064468043</v>
+        <v>0.01138460064468042</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -645,7 +645,7 @@
         <v>109.9883045323912</v>
       </c>
       <c r="E13" s="2">
-        <v>0.03300679589111741</v>
+        <v>0.03300679589111739</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -659,10 +659,10 @@
         <v>0.01325316684030718</v>
       </c>
       <c r="D14" s="2">
-        <v>110.1580605251441</v>
+        <v>110.1580605251442</v>
       </c>
       <c r="E14" s="2">
-        <v>0.01325316684030718</v>
+        <v>0.01325316684030717</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -676,10 +676,10 @@
         <v>0.01124827819464159</v>
       </c>
       <c r="D15" s="2">
-        <v>110.1457256168669</v>
+        <v>110.1457256168668</v>
       </c>
       <c r="E15" s="2">
-        <v>0.0112482781946416</v>
+        <v>0.01124827819464159</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -690,13 +690,13 @@
         <v>12</v>
       </c>
       <c r="C16" s="2">
-        <v>0.005586192634830428</v>
+        <v>0.005586192634830427</v>
       </c>
       <c r="D16" s="2">
         <v>110.0932410624208</v>
       </c>
       <c r="E16" s="2">
-        <v>0.005586192634830429</v>
+        <v>0.005586192634830425</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -707,13 +707,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="2">
-        <v>0.007446850214976573</v>
+        <v>0.007446850214976574</v>
       </c>
       <c r="D17" s="2">
         <v>110.3328749336861</v>
       </c>
       <c r="E17" s="2">
-        <v>0.007446850214976574</v>
+        <v>0.00744685021497657</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -730,7 +730,7 @@
         <v>120.0572480224469</v>
       </c>
       <c r="E18" s="2">
-        <v>0.06092800000000004</v>
+        <v>0.060928</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -747,7 +747,7 @@
         <v>119.1218955095635</v>
       </c>
       <c r="E19" s="2">
-        <v>0.04587188635795823</v>
+        <v>0.0458718863579582</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -764,7 +764,7 @@
         <v>120.1881949917042</v>
       </c>
       <c r="E20" s="2">
-        <v>0.006867916953228526</v>
+        <v>0.00686791695322852</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -781,7 +781,7 @@
         <v>117.0100602488289</v>
       </c>
       <c r="E21" s="2">
-        <v>0.01242696165087842</v>
+        <v>0.01242696165087841</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -798,7 +798,7 @@
         <v>116.7243620218604</v>
       </c>
       <c r="E22" s="2">
-        <v>0.008264052251417242</v>
+        <v>0.008264052251417237</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -815,7 +815,7 @@
         <v>117.0895973034999</v>
       </c>
       <c r="E23" s="2">
-        <v>0.008433296375534223</v>
+        <v>0.008433296375534218</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -832,7 +832,7 @@
         <v>114.1559714932755</v>
       </c>
       <c r="E24" s="2">
-        <v>0.004622845622821836</v>
+        <v>0.004622845622821834</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -849,7 +849,7 @@
         <v>121.0364820775794</v>
       </c>
       <c r="E25" s="2">
-        <v>0.005262293317993987</v>
+        <v>0.005262293317993983</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -866,7 +866,7 @@
         <v>112.7845110465006</v>
       </c>
       <c r="E26" s="2">
-        <v>0.08053580000000003</v>
+        <v>0.08053579999999998</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -877,13 +877,13 @@
         <v>7</v>
       </c>
       <c r="C27" s="2">
-        <v>0.06456028312613256</v>
+        <v>0.06456028312613257</v>
       </c>
       <c r="D27" s="2">
         <v>112.8741680619668</v>
       </c>
       <c r="E27" s="2">
-        <v>0.06456028312613257</v>
+        <v>0.06456028312613254</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -900,7 +900,7 @@
         <v>114.5739150383538</v>
       </c>
       <c r="E28" s="2">
-        <v>0.01057792999128234</v>
+        <v>0.01057792999128233</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -917,7 +917,7 @@
         <v>113.3627282107537</v>
       </c>
       <c r="E29" s="2">
-        <v>0.02351244717031737</v>
+        <v>0.02351244717031735</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -934,7 +934,7 @@
         <v>113.5187888506457</v>
       </c>
       <c r="E30" s="2">
-        <v>0.0113100384172708</v>
+        <v>0.01131003841727079</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -951,7 +951,7 @@
         <v>111.0540275479848</v>
       </c>
       <c r="E31" s="2">
-        <v>0.008638432376667015</v>
+        <v>0.00863843237666701</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -962,13 +962,13 @@
         <v>12</v>
       </c>
       <c r="C32" s="2">
-        <v>0.005718118764201594</v>
+        <v>0.005718118764201593</v>
       </c>
       <c r="D32" s="2">
-        <v>114.2437223327531</v>
+        <v>114.243722332753</v>
       </c>
       <c r="E32" s="2">
-        <v>0.005718118764201595</v>
+        <v>0.00571811876420159</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -985,7 +985,7 @@
         <v>114.1369314044013</v>
       </c>
       <c r="E33" s="2">
-        <v>0.009683988507077402</v>
+        <v>0.009683988507077397</v>
       </c>
     </row>
   </sheetData>
